--- a/data/intel/intel-01721078000168-lcm-contrucoes-ltda-2026-07-11.xlsx
+++ b/data/intel/intel-01721078000168-lcm-contrucoes-ltda-2026-07-11.xlsx
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>11/07/2026 12:46:22</t>
+          <t>11/07/2026 13:32:41</t>
         </is>
       </c>
     </row>
